--- a/src/assets/EQUIPOS.xlsx
+++ b/src/assets/EQUIPOS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98970F63-6F33-47B2-B909-65DFE29E5917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A94719-7F59-4FC5-97BB-A8FBB483E3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="665">
   <si>
     <t>Etiqueta</t>
   </si>
@@ -1568,12 +1568,6 @@
     <t>CROWNCUN\calidadcun</t>
   </si>
   <si>
-    <t>CROWNCUN\asistenterh</t>
-  </si>
-  <si>
-    <t>CROWNCUN\capacitacion</t>
-  </si>
-  <si>
     <t>CROWNCUN\gtecapacitacion</t>
   </si>
   <si>
@@ -1670,15 +1664,6 @@
     <t>ARRIVA\lavanderiacun</t>
   </si>
   <si>
-    <t>CROWNCUN\asistmanto</t>
-  </si>
-  <si>
-    <t>CROWNCUN\mantenimientocun</t>
-  </si>
-  <si>
-    <t>CROWNCUN\mantenimiento</t>
-  </si>
-  <si>
     <t>ARRIVA\gtemantocun</t>
   </si>
   <si>
@@ -1721,18 +1706,12 @@
     <t>Monitor camaras</t>
   </si>
   <si>
-    <t>LOCAL\lockservice</t>
-  </si>
-  <si>
     <t>Lock Service 1</t>
   </si>
   <si>
     <t>Lock Service 2</t>
   </si>
   <si>
-    <t>LOCAL\locklink</t>
-  </si>
-  <si>
     <t>Monitor Elevadores</t>
   </si>
   <si>
@@ -1742,9 +1721,6 @@
     <t>Monitor Camaras 2</t>
   </si>
   <si>
-    <t>LOCAL\seguridad</t>
-  </si>
-  <si>
     <t>CROWNCUN\seguridadcun</t>
   </si>
   <si>
@@ -1775,13 +1751,7 @@
     <t>Asistente Golden</t>
   </si>
   <si>
-    <t>LOCAL\sala de ventas</t>
-  </si>
-  <si>
     <t>Asistente operativo</t>
-  </si>
-  <si>
-    <t>LOCAL\atencion a socios</t>
   </si>
   <si>
     <t>Canales internos</t>
@@ -2049,6 +2019,21 @@
   </si>
   <si>
     <t>ARRIVA\apublicascun</t>
+  </si>
+  <si>
+    <t>ARRIVA\asismantocun</t>
+  </si>
+  <si>
+    <t>ARRIVA\mantenimientocun</t>
+  </si>
+  <si>
+    <t>ARRIVA\mantenimientocun02</t>
+  </si>
+  <si>
+    <t>ARRIA\asiscpcun</t>
+  </si>
+  <si>
+    <t>ARRIVA\asiscapcun</t>
   </si>
 </sst>
 </file>
@@ -2356,7 +2341,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EF8ACE9A-3DC4-4577-9E29-4CEAA3B671E9}" name="Tabla1" displayName="Tabla1" ref="A1:U102" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:U102" xr:uid="{EF8ACE9A-3DC4-4577-9E29-4CEAA3B671E9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U102">
-    <sortCondition ref="E1:E102"/>
+    <sortCondition ref="M1:M102"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{59771C38-00B0-4DC3-A168-A8045865F88D}" name="Etiqueta" dataDxfId="20"/>
@@ -2780,144 +2765,151 @@
         <v>11</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>337</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>436</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>621</v>
+      </c>
       <c r="L2" s="3" t="s">
-        <v>666</v>
+        <v>310</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>27</v>
+        <v>310</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="O2" t="s">
+        <v>141</v>
+      </c>
       <c r="P2" s="3" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="R2" s="16" t="s">
-        <v>634</v>
+        <v>605</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>625</v>
       </c>
       <c r="S2" s="13">
-        <v>44829</v>
+        <v>45513</v>
       </c>
       <c r="T2" s="13">
-        <v>45194</v>
+        <v>46607</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>343</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>25</v>
+        <v>502</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="3"/>
+        <v>330</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="L3" s="3" t="s">
-        <v>666</v>
+        <v>310</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>27</v>
+        <v>310</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="O3" t="s">
+        <v>142</v>
+      </c>
       <c r="P3" s="3" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="S3" s="13">
-        <v>45563</v>
+        <v>44781</v>
       </c>
       <c r="T3" s="13">
-        <v>45563</v>
+        <v>45876</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="3" t="s">
-        <v>337</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>436</v>
+        <v>508</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>14</v>
@@ -2926,13 +2918,14 @@
         <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>219</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="I4" s="21"/>
       <c r="J4" s="3" t="s">
-        <v>631</v>
+        <v>657</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>310</v>
@@ -2944,39 +2937,39 @@
         <v>20</v>
       </c>
       <c r="O4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="S4" s="13">
-        <v>45513</v>
+        <v>44772</v>
       </c>
       <c r="T4" s="13">
-        <v>46607</v>
+        <v>45867</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>14</v>
@@ -2988,10 +2981,10 @@
         <v>330</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>310</v>
@@ -3003,36 +2996,36 @@
         <v>20</v>
       </c>
       <c r="O5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="S5" s="13">
-        <v>44781</v>
+        <v>44441</v>
       </c>
       <c r="T5" s="13">
-        <v>45876</v>
+        <v>45537</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>508</v>
+        <v>438</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>14</v>
@@ -3041,14 +3034,13 @@
         <v>15</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="I6" s="21"/>
+        <v>224</v>
+      </c>
       <c r="J6" s="3" t="s">
-        <v>667</v>
+        <v>507</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>310</v>
@@ -3060,54 +3052,54 @@
         <v>20</v>
       </c>
       <c r="O6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="S6" s="13">
-        <v>44772</v>
+        <v>45468</v>
       </c>
       <c r="T6" s="13">
-        <v>45867</v>
+        <v>46562</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>505</v>
+        <v>437</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>310</v>
@@ -3115,114 +3107,106 @@
       <c r="M7" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="8" t="s">
         <v>20</v>
       </c>
       <c r="O7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="S7" s="13">
-        <v>44441</v>
+        <v>45516</v>
       </c>
       <c r="T7" s="13">
-        <v>45537</v>
+        <v>46610</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" spans="1:21">
+      <c r="A8" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="B8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>16</v>
+        <v>424</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O8" t="s">
-        <v>146</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="Q8" s="3" t="s">
+      <c r="O8"/>
+      <c r="S8" s="13">
+        <v>45057</v>
+      </c>
+      <c r="T8" s="13">
+        <v>46149</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>635</v>
-      </c>
-      <c r="S8" s="13">
-        <v>45468</v>
-      </c>
-      <c r="T8" s="13">
-        <v>46562</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>439</v>
+        <v>510</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>305</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>424</v>
+        <v>16</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>509</v>
+        <v>582</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>311</v>
@@ -3233,29 +3217,40 @@
       <c r="N9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O9"/>
+      <c r="O9" t="s">
+        <v>147</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="R9" s="17" t="s">
+        <v>630</v>
+      </c>
       <c r="S9" s="13">
-        <v>45057</v>
+        <v>45119</v>
       </c>
       <c r="T9" s="13">
-        <v>46149</v>
+        <v>46214</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>14</v>
@@ -3267,10 +3262,10 @@
         <v>16</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>592</v>
+        <v>513</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>311</v>
@@ -3282,54 +3277,54 @@
         <v>20</v>
       </c>
       <c r="O10" t="s">
-        <v>147</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>617</v>
+        <v>149</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="S10" s="13">
-        <v>45119</v>
+        <v>45016</v>
       </c>
       <c r="T10" s="13">
-        <v>46214</v>
+        <v>46111</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>16</v>
+        <v>350</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>513</v>
+        <v>583</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>311</v>
@@ -3341,92 +3336,95 @@
         <v>20</v>
       </c>
       <c r="O11" t="s">
-        <v>149</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>616</v>
+        <v>148</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>608</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="S11" s="13">
-        <v>45016</v>
+        <v>45026</v>
       </c>
       <c r="T11" s="13">
-        <v>46111</v>
+        <v>46121</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="3" t="s">
-        <v>355</v>
-      </c>
       <c r="B12" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>517</v>
+        <v>229</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>514</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O12" t="s">
-        <v>152</v>
+        <v>150</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="S12" s="13">
-        <v>44707</v>
+        <v>44716</v>
       </c>
       <c r="T12" s="13">
-        <v>45802</v>
+        <v>45811</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>14</v>
@@ -3435,13 +3433,13 @@
         <v>15</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>518</v>
+        <v>663</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>314</v>
@@ -3453,39 +3451,33 @@
         <v>20</v>
       </c>
       <c r="O13" t="s">
-        <v>153</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>615</v>
+        <v>152</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="S13" s="13">
-        <v>45012</v>
+        <v>44707</v>
       </c>
       <c r="T13" s="13">
-        <v>46107</v>
+        <v>45802</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>14</v>
@@ -3494,13 +3486,13 @@
         <v>15</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>523</v>
+        <v>664</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>314</v>
@@ -3512,39 +3504,39 @@
         <v>20</v>
       </c>
       <c r="O14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="S14" s="13">
-        <v>44833</v>
+        <v>45012</v>
       </c>
       <c r="T14" s="13">
-        <v>45928</v>
+        <v>46107</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="3" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>14</v>
@@ -3553,234 +3545,232 @@
         <v>15</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>498</v>
+        <v>237</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>521</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O15" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="S15" s="13">
-        <v>45498</v>
+        <v>44833</v>
       </c>
       <c r="T15" s="13">
-        <v>46595</v>
+        <v>45928</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="3" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O16" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="S16" s="13">
-        <v>44442</v>
+        <v>44667</v>
       </c>
       <c r="T16" s="13">
-        <v>45537</v>
+        <v>45762</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="3" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>429</v>
+        <v>518</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>16</v>
+        <v>350</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O17" t="s">
-        <v>135</v>
-      </c>
+      <c r="O17"/>
       <c r="P17" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="S17" s="13">
-        <v>45498</v>
+        <v>45517</v>
       </c>
       <c r="T17" s="13">
-        <v>46592</v>
+        <v>46611</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>531</v>
+        <v>236</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O18" t="s">
-        <v>161</v>
+        <v>585</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="S18" s="13">
-        <v>44439</v>
+        <v>45873</v>
       </c>
       <c r="T18" s="13">
-        <v>45534</v>
+        <v>46968</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="3" t="s">
-        <v>369</v>
+        <v>12</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>14</v>
@@ -3792,13 +3782,13 @@
         <v>16</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>532</v>
+        <v>17</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>498</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>316</v>
+        <v>18</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>19</v>
@@ -3807,39 +3797,39 @@
         <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R19" s="17" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="S19" s="13">
-        <v>45020</v>
+        <v>45498</v>
       </c>
       <c r="T19" s="13">
-        <v>46115</v>
+        <v>46595</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="3" t="s">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>14</v>
@@ -3848,16 +3838,16 @@
         <v>15</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>316</v>
+        <v>18</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>19</v>
@@ -3866,39 +3856,39 @@
         <v>20</v>
       </c>
       <c r="O20" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R20" s="17" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="S20" s="13">
-        <v>45020</v>
+        <v>44442</v>
       </c>
       <c r="T20" s="13">
-        <v>46115</v>
+        <v>45537</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="3" t="s">
-        <v>372</v>
+        <v>331</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>536</v>
+        <v>429</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>14</v>
@@ -3907,16 +3897,16 @@
         <v>15</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>317</v>
+        <v>18</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>19</v>
@@ -3925,36 +3915,39 @@
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R21" s="17" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="S21" s="13">
-        <v>44701</v>
+        <v>45498</v>
       </c>
       <c r="T21" s="13">
-        <v>45796</v>
+        <v>46592</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="22" spans="1:21">
+      <c r="A22" s="3" t="s">
+        <v>368</v>
+      </c>
       <c r="B22" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>14</v>
@@ -3966,13 +3959,13 @@
         <v>330</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>19</v>
@@ -3981,37 +3974,39 @@
         <v>20</v>
       </c>
       <c r="O22" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="S22" s="13">
-        <v>44657</v>
+        <v>44439</v>
       </c>
       <c r="T22" s="13">
-        <v>45752</v>
+        <v>45534</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>453</v>
+      </c>
       <c r="D23" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>14</v>
@@ -4020,14 +4015,16 @@
         <v>15</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>366</v>
+        <v>16</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J23" s="3"/>
+        <v>244</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>530</v>
+      </c>
       <c r="L23" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>19</v>
@@ -4035,32 +4032,40 @@
       <c r="N23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O23"/>
+      <c r="O23" t="s">
+        <v>162</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>605</v>
+      </c>
       <c r="R23" s="17" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="S23" s="13">
-        <v>43580</v>
+        <v>45020</v>
       </c>
       <c r="T23" s="13">
-        <v>44700</v>
+        <v>46115</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>534</v>
+        <v>443</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>14</v>
@@ -4069,16 +4074,16 @@
         <v>15</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>335</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>19</v>
@@ -4087,37 +4092,39 @@
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="S24" s="13">
-        <v>45849</v>
+        <v>45020</v>
       </c>
       <c r="T24" s="13">
-        <v>46944</v>
+        <v>46115</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>534</v>
+      </c>
       <c r="D25" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>14</v>
@@ -4129,10 +4136,10 @@
         <v>330</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>317</v>
@@ -4144,39 +4151,36 @@
         <v>20</v>
       </c>
       <c r="O25" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R25" s="17" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="S25" s="13">
-        <v>44446</v>
+        <v>44701</v>
       </c>
       <c r="T25" s="13">
-        <v>45541</v>
+        <v>45796</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="B26" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>14</v>
@@ -4185,13 +4189,13 @@
         <v>15</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>317</v>
@@ -4203,39 +4207,37 @@
         <v>20</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R26" s="17" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="S26" s="13">
-        <v>45012</v>
+        <v>44657</v>
       </c>
       <c r="T26" s="13">
-        <v>46107</v>
+        <v>45752</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>461</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C27" s="4"/>
       <c r="D27" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>14</v>
@@ -4244,14 +4246,12 @@
         <v>15</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>548</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="J27" s="3"/>
       <c r="L27" s="3" t="s">
         <v>317</v>
       </c>
@@ -4261,40 +4261,32 @@
       <c r="N27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O27" t="s">
-        <v>173</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>615</v>
-      </c>
+      <c r="O27"/>
       <c r="R27" s="17" t="s">
         <v>638</v>
       </c>
       <c r="S27" s="13">
-        <v>44664</v>
+        <v>43580</v>
       </c>
       <c r="T27" s="13">
-        <v>45759</v>
+        <v>44700</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>462</v>
+        <v>532</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>14</v>
@@ -4303,13 +4295,13 @@
         <v>15</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>16</v>
+        <v>335</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>317</v>
@@ -4321,39 +4313,37 @@
         <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R28" s="19" t="s">
-        <v>640</v>
+        <v>605</v>
+      </c>
+      <c r="R28" s="17" t="s">
+        <v>627</v>
       </c>
       <c r="S28" s="13">
-        <v>45386</v>
+        <v>45849</v>
       </c>
       <c r="T28" s="13">
-        <v>46115</v>
+        <v>46944</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="3" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>469</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C29" s="4"/>
       <c r="D29" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>14</v>
@@ -4365,10 +4355,10 @@
         <v>330</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>317</v>
@@ -4380,36 +4370,39 @@
         <v>20</v>
       </c>
       <c r="O29" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R29" s="17" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="S29" s="13">
-        <v>44377</v>
+        <v>44446</v>
       </c>
       <c r="T29" s="13">
-        <v>45472</v>
+        <v>45541</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="30" spans="1:21">
+      <c r="A30" s="3" t="s">
+        <v>378</v>
+      </c>
       <c r="B30" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>14</v>
@@ -4418,16 +4411,16 @@
         <v>15</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>335</v>
+        <v>16</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>665</v>
+        <v>542</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>26</v>
+        <v>317</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>19</v>
@@ -4436,39 +4429,39 @@
         <v>20</v>
       </c>
       <c r="O30" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R30" s="15" t="s">
-        <v>637</v>
+        <v>605</v>
+      </c>
+      <c r="R30" s="17" t="s">
+        <v>630</v>
       </c>
       <c r="S30" s="13">
-        <v>45894</v>
+        <v>45012</v>
       </c>
       <c r="T30" s="13">
-        <v>46989</v>
+        <v>46107</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="3" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>430</v>
+        <v>461</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>14</v>
@@ -4477,54 +4470,57 @@
         <v>15</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>630</v>
+        <v>546</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O31" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="S31" s="13">
-        <v>45498</v>
+        <v>44664</v>
       </c>
       <c r="T31" s="13">
-        <v>46592</v>
+        <v>45759</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" spans="1:21">
+      <c r="A32" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>14</v>
@@ -4536,54 +4532,54 @@
         <v>16</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>501</v>
+        <v>547</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O32" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R32" s="17" t="s">
-        <v>635</v>
+        <v>605</v>
+      </c>
+      <c r="R32" s="19" t="s">
+        <v>630</v>
       </c>
       <c r="S32" s="13">
-        <v>45498</v>
+        <v>45386</v>
       </c>
       <c r="T32" s="13">
-        <v>46592</v>
+        <v>46115</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="3" t="s">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>14</v>
@@ -4592,57 +4588,54 @@
         <v>15</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>632</v>
+        <v>551</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O33" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R33" s="17" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="S33" s="13">
-        <v>45519</v>
+        <v>44377</v>
       </c>
       <c r="T33" s="13">
-        <v>46613</v>
+        <v>45472</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="3" t="s">
-        <v>334</v>
-      </c>
       <c r="B34" s="3" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>433</v>
+        <v>480</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>14</v>
@@ -4654,523 +4647,506 @@
         <v>335</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>668</v>
+        <v>26</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O34" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R34" s="17" t="s">
-        <v>637</v>
+        <v>605</v>
+      </c>
+      <c r="R34" s="15" t="s">
+        <v>627</v>
       </c>
       <c r="S34" s="13">
-        <v>45849</v>
+        <v>45894</v>
       </c>
       <c r="T34" s="13">
-        <v>46944</v>
+        <v>46989</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="B35" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>449</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="C35" s="4"/>
       <c r="D35" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>525</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O35" t="s">
-        <v>156</v>
+      <c r="O35" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="R35" s="18" t="s">
-        <v>663</v>
+        <v>605</v>
       </c>
       <c r="S35" s="13">
-        <v>45021</v>
+        <v>43526</v>
       </c>
       <c r="T35" s="13">
-        <v>46116</v>
+        <v>44641</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" s="3" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O36" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R36" s="17" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="S36" s="13">
-        <v>45883</v>
+        <v>45762</v>
       </c>
       <c r="T36" s="13">
-        <v>46978</v>
+        <v>46857</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="B37" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O37" t="s">
-        <v>158</v>
-      </c>
+      <c r="O37"/>
       <c r="P37" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R37" s="17" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="S37" s="13">
-        <v>44453</v>
+        <v>45058</v>
       </c>
       <c r="T37" s="13">
-        <v>44817</v>
+        <v>46153</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="3" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>67</v>
+        <v>338</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>241</v>
+        <v>342</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>529</v>
+        <v>581</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O38" t="s">
-        <v>159</v>
+      <c r="O38" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R38" s="17" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="S38" s="13">
-        <v>43605</v>
+        <v>45514</v>
       </c>
       <c r="T38" s="13">
-        <v>44700</v>
+        <v>46608</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>16</v>
+        <v>360</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>315</v>
+        <v>210</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>160</v>
+        <v>586</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R39" s="17" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="S39" s="13">
-        <v>45099</v>
+        <v>45856</v>
       </c>
       <c r="T39" s="13">
-        <v>46194</v>
+        <v>46951</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="3" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R40" s="17" t="s">
-        <v>653</v>
+        <v>634</v>
       </c>
       <c r="S40" s="13">
-        <v>44183</v>
+        <v>45518</v>
       </c>
       <c r="T40" s="13">
-        <v>45277</v>
+        <v>46612</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="3" t="s">
-        <v>392</v>
-      </c>
       <c r="B41" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41"/>
+      <c r="P41" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="S41" s="13">
+        <v>43755</v>
+      </c>
+      <c r="T41" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O41" t="s">
-        <v>182</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R41" s="17" t="s">
-        <v>653</v>
-      </c>
-      <c r="S41" s="13">
-        <v>44189</v>
-      </c>
-      <c r="T41" s="13">
-        <v>45283</v>
-      </c>
       <c r="U41" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="3" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O42" t="s">
-        <v>183</v>
+        <v>589</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R42" s="18" t="s">
-        <v>664</v>
+        <v>605</v>
+      </c>
+      <c r="R42" s="15" t="s">
+        <v>629</v>
       </c>
       <c r="S42" s="13">
-        <v>45849</v>
+        <v>45513</v>
       </c>
       <c r="T42" s="13">
-        <v>46944</v>
+        <v>46607</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="3" t="s">
-        <v>394</v>
+        <v>332</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>474</v>
+        <v>430</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>14</v>
@@ -5182,13 +5158,13 @@
         <v>16</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>561</v>
+        <v>620</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>319</v>
@@ -5197,39 +5173,36 @@
         <v>20</v>
       </c>
       <c r="O43" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R43" s="17" t="s">
-        <v>654</v>
+        <v>625</v>
       </c>
       <c r="S43" s="13">
-        <v>45958</v>
+        <v>45498</v>
       </c>
       <c r="T43" s="13">
-        <v>47053</v>
+        <v>46592</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="3" t="s">
-        <v>395</v>
-      </c>
       <c r="B44" s="3" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>472</v>
+        <v>431</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>14</v>
@@ -5238,16 +5211,16 @@
         <v>15</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>366</v>
+        <v>16</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>562</v>
+        <v>501</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>319</v>
@@ -5256,39 +5229,39 @@
         <v>20</v>
       </c>
       <c r="O44" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R44" s="17" t="s">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="S44" s="13">
-        <v>43580</v>
+        <v>45498</v>
       </c>
       <c r="T44" s="13">
-        <v>44700</v>
+        <v>46592</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="3" t="s">
-        <v>396</v>
+        <v>333</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>14</v>
@@ -5297,16 +5270,16 @@
         <v>15</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>335</v>
+        <v>16</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>559</v>
+        <v>622</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>319</v>
@@ -5315,39 +5288,39 @@
         <v>20</v>
       </c>
       <c r="O45" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R45" s="17" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="S45" s="13">
-        <v>45849</v>
+        <v>45519</v>
       </c>
       <c r="T45" s="13">
-        <v>46944</v>
+        <v>46613</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="3" t="s">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>14</v>
@@ -5356,16 +5329,16 @@
         <v>15</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>16</v>
+        <v>335</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>558</v>
+        <v>659</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>324</v>
+        <v>658</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>319</v>
@@ -5374,39 +5347,39 @@
         <v>20</v>
       </c>
       <c r="O46" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R46" s="17" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="S46" s="13">
-        <v>45012</v>
+        <v>45849</v>
       </c>
       <c r="T46" s="13">
-        <v>46107</v>
+        <v>46944</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="3" t="s">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>14</v>
@@ -5418,13 +5391,13 @@
         <v>16</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>319</v>
@@ -5433,52 +5406,57 @@
         <v>20</v>
       </c>
       <c r="O47" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R47" s="17" t="s">
-        <v>635</v>
+        <v>609</v>
+      </c>
+      <c r="R47" s="18" t="s">
+        <v>653</v>
       </c>
       <c r="S47" s="13">
-        <v>45537</v>
+        <v>45021</v>
       </c>
       <c r="T47" s="13">
-        <v>46631</v>
+        <v>46116</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="48" spans="1:21">
+      <c r="A48" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="B48" s="3" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>567</v>
+        <v>450</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>305</v>
+        <v>15</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>402</v>
+        <v>335</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J48" s="3"/>
+        <v>239</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>524</v>
+      </c>
       <c r="L48" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>319</v>
@@ -5487,46 +5465,54 @@
         <v>20</v>
       </c>
       <c r="O48" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
+      </c>
+      <c r="R48" s="17" t="s">
+        <v>627</v>
       </c>
       <c r="S48" s="13">
-        <v>45146</v>
+        <v>45883</v>
       </c>
       <c r="T48" s="13">
-        <v>46256</v>
+        <v>46978</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="B49" s="3" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>572</v>
+        <v>525</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="H49" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="J49" s="3" t="s">
-        <v>573</v>
+        <v>526</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>319</v>
@@ -5535,39 +5521,57 @@
         <v>20</v>
       </c>
       <c r="O49" t="s">
-        <v>193</v>
+        <v>158</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="R49" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="S49" s="13">
+        <v>44453</v>
+      </c>
+      <c r="T49" s="13">
+        <v>44817</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
     </row>
     <row r="50" spans="1:21">
+      <c r="A50" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="B50" s="3" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>574</v>
+        <v>451</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>305</v>
+        <v>15</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>402</v>
+        <v>366</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>575</v>
+        <v>527</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>319</v>
@@ -5576,27 +5580,39 @@
         <v>20</v>
       </c>
       <c r="O50" t="s">
-        <v>194</v>
+        <v>159</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R50" s="17" t="s">
+        <v>638</v>
       </c>
       <c r="S50" s="13">
-        <v>45471</v>
+        <v>43605</v>
       </c>
       <c r="T50" s="13">
-        <v>46607</v>
+        <v>44700</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="51" spans="1:21">
+      <c r="A51" s="3" t="s">
+        <v>367</v>
+      </c>
       <c r="B51" s="3" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>14</v>
@@ -5605,16 +5621,16 @@
         <v>15</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>576</v>
+        <v>528</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>319</v>
@@ -5623,39 +5639,39 @@
         <v>20</v>
       </c>
       <c r="O51" t="s">
-        <v>598</v>
+        <v>160</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R51" s="15" t="s">
-        <v>638</v>
+        <v>605</v>
+      </c>
+      <c r="R51" s="17" t="s">
+        <v>630</v>
       </c>
       <c r="S51" s="13">
-        <v>44699</v>
+        <v>45099</v>
       </c>
       <c r="T51" s="13">
-        <v>45794</v>
+        <v>46194</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52" s="3" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>14</v>
@@ -5664,16 +5680,16 @@
         <v>15</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>319</v>
@@ -5682,57 +5698,57 @@
         <v>20</v>
       </c>
       <c r="O52" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R52" s="17" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="S52" s="13">
-        <v>43580</v>
+        <v>44183</v>
       </c>
       <c r="T52" s="13">
-        <v>44700</v>
+        <v>45277</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="3" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>305</v>
+        <v>15</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>582</v>
+        <v>552</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M53" s="3" t="s">
         <v>319</v>
@@ -5741,33 +5757,39 @@
         <v>20</v>
       </c>
       <c r="O53" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
+      </c>
+      <c r="R53" s="17" t="s">
+        <v>643</v>
       </c>
       <c r="S53" s="13">
-        <v>43108</v>
+        <v>44189</v>
       </c>
       <c r="T53" s="13">
-        <v>43564</v>
+        <v>45283</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="54" spans="1:21">
+      <c r="A54" s="3" t="s">
+        <v>393</v>
+      </c>
       <c r="B54" s="3" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>585</v>
+        <v>473</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>14</v>
@@ -5776,54 +5798,57 @@
         <v>15</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>16</v>
+        <v>335</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="J54" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O54" t="s">
+        <v>183</v>
+      </c>
+      <c r="P54" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O54" t="s">
-        <v>204</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>616</v>
-      </c>
       <c r="Q54" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R54" s="17" t="s">
-        <v>640</v>
+        <v>605</v>
+      </c>
+      <c r="R54" s="18" t="s">
+        <v>654</v>
       </c>
       <c r="S54" s="13">
-        <v>45112</v>
+        <v>45849</v>
       </c>
       <c r="T54" s="13">
-        <v>46207</v>
+        <v>46944</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="55" spans="1:21">
+      <c r="A55" s="3" t="s">
+        <v>394</v>
+      </c>
       <c r="B55" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>14</v>
@@ -5832,52 +5857,57 @@
         <v>15</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N55" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O55"/>
+      <c r="O55" t="s">
+        <v>184</v>
+      </c>
       <c r="P55" s="3" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R55" s="17" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="S55" s="13">
-        <v>44697</v>
+        <v>45958</v>
       </c>
       <c r="T55" s="13">
-        <v>45792</v>
+        <v>47053</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="56" spans="1:21">
+      <c r="A56" s="3" t="s">
+        <v>395</v>
+      </c>
       <c r="B56" s="3" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>587</v>
+        <v>472</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>14</v>
@@ -5886,155 +5916,175 @@
         <v>15</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>16</v>
+        <v>366</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>607</v>
+        <v>557</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O56" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R56" s="17" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="S56" s="13">
-        <v>45349</v>
+        <v>43580</v>
       </c>
       <c r="T56" s="13">
-        <v>46444</v>
+        <v>44700</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="57" spans="1:21">
+      <c r="A57" s="3" t="s">
+        <v>396</v>
+      </c>
       <c r="B57" s="3" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>589</v>
+        <v>471</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>305</v>
+        <v>15</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>662</v>
+        <v>335</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>609</v>
+        <v>554</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O57"/>
+      <c r="O57" t="s">
+        <v>186</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R57" s="17" t="s">
+        <v>627</v>
+      </c>
       <c r="S57" s="13">
-        <v>43112</v>
+        <v>45849</v>
       </c>
       <c r="T57" s="13">
-        <v>43598</v>
+        <v>46944</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="58" spans="1:21">
+      <c r="A58" s="3" t="s">
+        <v>397</v>
+      </c>
       <c r="B58" s="3" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>305</v>
+        <v>15</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>415</v>
+        <v>16</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O58" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
+      </c>
+      <c r="R58" s="17" t="s">
+        <v>630</v>
       </c>
       <c r="S58" s="13">
-        <v>43066</v>
+        <v>45012</v>
       </c>
       <c r="T58" s="13">
-        <v>43522</v>
+        <v>46107</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>14</v>
@@ -6043,234 +6093,186 @@
         <v>15</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O59" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R59" s="19" t="s">
-        <v>638</v>
+        <v>605</v>
+      </c>
+      <c r="R59" s="17" t="s">
+        <v>625</v>
       </c>
       <c r="S59" s="13">
-        <v>44699</v>
+        <v>45537</v>
       </c>
       <c r="T59" s="13">
-        <v>45794</v>
+        <v>46631</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="60" spans="1:21">
-      <c r="A60" s="3" t="s">
-        <v>387</v>
-      </c>
       <c r="B60" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>465</v>
+        <v>562</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>16</v>
+        <v>402</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>552</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="J60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O60" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R60" s="19" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
       <c r="S60" s="13">
-        <v>45118</v>
+        <v>45146</v>
       </c>
       <c r="T60" s="13">
-        <v>46213</v>
+        <v>46256</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="61" spans="1:21">
-      <c r="A61" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="B61" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>466</v>
+        <v>565</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>553</v>
+        <v>308</v>
+      </c>
+      <c r="H61" s="1"/>
+      <c r="J61" s="3" t="s">
+        <v>566</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O61" t="s">
-        <v>178</v>
-      </c>
-      <c r="P61" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q61" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R61" s="19" t="s">
-        <v>640</v>
-      </c>
-      <c r="S61" s="13">
-        <v>45099</v>
-      </c>
-      <c r="T61" s="13">
-        <v>46194</v>
+        <v>193</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
     </row>
     <row r="62" spans="1:21">
-      <c r="A62" s="3" t="s">
-        <v>390</v>
-      </c>
       <c r="B62" s="3" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>468</v>
+        <v>567</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>330</v>
+        <v>402</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>555</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="J62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O62" t="s">
-        <v>180</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R62" s="17" t="s">
-        <v>638</v>
+        <v>194</v>
       </c>
       <c r="S62" s="13">
-        <v>44664</v>
+        <v>45471</v>
       </c>
       <c r="T62" s="13">
-        <v>45759</v>
+        <v>46607</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="63" spans="1:21">
-      <c r="A63" s="3" t="s">
-        <v>409</v>
-      </c>
       <c r="B63" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>14</v>
@@ -6279,57 +6281,57 @@
         <v>15</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O63" t="s">
-        <v>197</v>
+        <v>588</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R63" s="15" t="s">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="S63" s="13">
-        <v>45264</v>
+        <v>44699</v>
       </c>
       <c r="T63" s="13">
-        <v>46359</v>
+        <v>45794</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>14</v>
@@ -6338,291 +6340,261 @@
         <v>15</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>579</v>
+        <v>522</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O64" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R64" s="17" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="S64" s="13">
-        <v>45264</v>
+        <v>43580</v>
       </c>
       <c r="T64" s="13">
-        <v>46389</v>
+        <v>44700</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="3" t="s">
-        <v>336</v>
+        <v>416</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J65" s="3"/>
+        <v>292</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="L65" s="3" t="s">
-        <v>496</v>
+        <v>328</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>27</v>
+        <v>319</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O65" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="R65" s="17" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="S65" s="13">
-        <v>45895</v>
+        <v>43108</v>
       </c>
       <c r="T65" s="13">
-        <v>46990</v>
+        <v>43564</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="3" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>564</v>
+        <v>352</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>543</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O66" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R66" s="17" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="S66" s="13">
-        <v>45539</v>
+        <v>44664</v>
       </c>
       <c r="T66" s="13">
-        <v>46633</v>
+        <v>45759</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>477</v>
+        <v>563</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>15</v>
+        <v>306</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>565</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="J67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O67" t="s">
-        <v>190</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="Q67" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="R67" s="17" t="s">
-        <v>635</v>
-      </c>
+      <c r="O67"/>
       <c r="S67" s="13">
-        <v>45547</v>
+        <v>45757</v>
       </c>
       <c r="T67" s="13">
-        <v>46641</v>
+        <v>46852</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="68" spans="1:21">
-      <c r="A68" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="B68" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>488</v>
+        <v>564</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>16</v>
+        <v>405</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>583</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="J68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O68" t="s">
-        <v>203</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="Q68" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="R68" s="17" t="s">
-        <v>635</v>
+      <c r="O68"/>
+      <c r="R68" s="1" t="s">
+        <v>646</v>
       </c>
       <c r="S68" s="13">
-        <v>45498</v>
+        <v>44425</v>
       </c>
       <c r="T68" s="13">
-        <v>46592</v>
+        <v>45520</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="69" spans="1:21">
-      <c r="A69" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="B69" s="3" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>437</v>
+        <v>326</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>133</v>
@@ -6631,57 +6603,51 @@
         <v>15</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>504</v>
+        <v>288</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="N69" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="N69" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O69" t="s">
-        <v>144</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q69" s="3" t="s">
-        <v>615</v>
+        <v>199</v>
       </c>
       <c r="R69" s="17" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="S69" s="13">
-        <v>45516</v>
+        <v>45265</v>
       </c>
       <c r="T69" s="13">
-        <v>46610</v>
+        <v>46360</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="3" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>511</v>
+        <v>459</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>133</v>
@@ -6690,337 +6656,312 @@
         <v>15</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>593</v>
+        <v>544</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O70" t="s">
-        <v>148</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>618</v>
+        <v>171</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="R70" s="17" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="S70" s="13">
-        <v>45026</v>
+        <v>45848</v>
       </c>
       <c r="T70" s="13">
-        <v>46121</v>
+        <v>46943</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="B71" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>440</v>
+        <v>577</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>352</v>
+        <v>16</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>514</v>
+        <v>296</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>596</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O71" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R71" s="17" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="S71" s="13">
-        <v>44716</v>
+        <v>45112</v>
       </c>
       <c r="T71" s="13">
-        <v>45811</v>
+        <v>46207</v>
       </c>
       <c r="U71" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
+      <c r="B72" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J72" s="3"/>
+      <c r="L72" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O72"/>
+      <c r="P72" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="R72" s="17" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="72" spans="1:21">
-      <c r="A72" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O72" t="s">
-        <v>154</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R72" s="17" t="s">
-        <v>642</v>
-      </c>
       <c r="S72" s="13">
-        <v>44667</v>
+        <v>44697</v>
       </c>
       <c r="T72" s="13">
-        <v>45762</v>
+        <v>45792</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="73" spans="1:21">
-      <c r="A73" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="B73" s="3" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>520</v>
+        <v>578</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>350</v>
+        <v>16</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>521</v>
+        <v>597</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O73"/>
+      <c r="O73" t="s">
+        <v>207</v>
+      </c>
       <c r="P73" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R73" s="17" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="S73" s="13">
-        <v>45517</v>
+        <v>45349</v>
       </c>
       <c r="T73" s="13">
-        <v>46611</v>
+        <v>46444</v>
       </c>
       <c r="U73" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="74" spans="1:21">
-      <c r="A74" s="3" t="s">
-        <v>359</v>
-      </c>
       <c r="B74" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>447</v>
+        <v>579</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>360</v>
+        <v>652</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>522</v>
+        <v>301</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>599</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O74" t="s">
-        <v>595</v>
-      </c>
-      <c r="P74" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q74" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R74" s="17" t="s">
-        <v>645</v>
-      </c>
+      <c r="O74"/>
       <c r="S74" s="13">
-        <v>45873</v>
+        <v>43112</v>
       </c>
       <c r="T74" s="13">
-        <v>46968</v>
+        <v>43598</v>
       </c>
       <c r="U74" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="B75" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C75" s="4"/>
+        <v>131</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>493</v>
+      </c>
       <c r="D75" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>305</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>422</v>
+        <v>415</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="J75" s="3"/>
       <c r="L75" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O75" s="5" t="s">
-        <v>421</v>
+      <c r="O75" t="s">
+        <v>209</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="S75" s="13">
-        <v>43526</v>
+        <v>43066</v>
       </c>
       <c r="T75" s="13">
-        <v>44641</v>
+        <v>43522</v>
       </c>
       <c r="U75" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="76" spans="1:21">
-      <c r="A76" s="3" t="s">
-        <v>353</v>
-      </c>
       <c r="B76" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>442</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="C76" s="4"/>
       <c r="D76" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>133</v>
@@ -7029,54 +6970,52 @@
         <v>15</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>516</v>
+        <v>598</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O76" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R76" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="S76" s="13">
-        <v>45762</v>
+        <v>45654</v>
       </c>
       <c r="T76" s="13">
-        <v>46857</v>
+        <v>46748</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="B77" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>542</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>133</v>
@@ -7085,55 +7024,54 @@
         <v>15</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>246</v>
+        <v>295</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>541</v>
+        <v>594</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O77"/>
-      <c r="P77" s="3" t="s">
-        <v>616</v>
+      <c r="O77" t="s">
+        <v>595</v>
+      </c>
+      <c r="P77" s="11" t="s">
+        <v>607</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R77" s="17" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="S77" s="13">
-        <v>45058</v>
+        <v>45419</v>
       </c>
       <c r="T77" s="13">
-        <v>46153</v>
+        <v>46513</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="78" spans="1:21">
-      <c r="A78" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="B78" s="3" t="s">
-        <v>338</v>
+        <v>125</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>133</v>
@@ -7142,57 +7080,54 @@
         <v>15</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>339</v>
+        <v>350</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O78" s="3" t="s">
-        <v>340</v>
+      <c r="O78" t="s">
+        <v>205</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R78" s="17" t="s">
         <v>650</v>
       </c>
       <c r="S78" s="13">
-        <v>45514</v>
+        <v>44697</v>
       </c>
       <c r="T78" s="13">
-        <v>46608</v>
+        <v>45792</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="79" spans="1:21">
-      <c r="A79" s="3" t="s">
-        <v>374</v>
-      </c>
       <c r="B79" s="3" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>455</v>
+        <v>491</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>133</v>
@@ -7201,333 +7136,346 @@
         <v>15</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>539</v>
+        <v>592</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O79" t="s">
-        <v>596</v>
+        <v>206</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R79" s="17" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="S79" s="13">
-        <v>45856</v>
+        <v>44705</v>
       </c>
       <c r="T79" s="13">
-        <v>46951</v>
+        <v>45800</v>
       </c>
       <c r="U79" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="80" spans="1:21">
-      <c r="A80" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="B80" s="3" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>456</v>
+        <v>580</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>133</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>350</v>
+        <v>418</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>540</v>
+        <v>610</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O80" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R80" s="17" t="s">
-        <v>644</v>
+        <v>609</v>
       </c>
       <c r="S80" s="13">
-        <v>45518</v>
+        <v>43427</v>
       </c>
       <c r="T80" s="13">
-        <v>46612</v>
+        <v>45272</v>
       </c>
       <c r="U80" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23">
+      <c r="A81" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O81" t="s">
+        <v>176</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R81" s="19" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="81" spans="1:23">
-      <c r="B81" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O81"/>
-      <c r="P81" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="S81" s="13">
-        <v>43755</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>633</v>
+        <v>44699</v>
+      </c>
+      <c r="T81" s="13">
+        <v>45794</v>
       </c>
       <c r="U81" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="82" spans="1:23">
       <c r="A82" s="3" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>345</v>
+        <v>16</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>577</v>
+        <v>262</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>661</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>26</v>
+        <v>323</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>19</v>
+        <v>323</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O82" t="s">
-        <v>599</v>
+        <v>177</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R82" s="15" t="s">
-        <v>639</v>
+        <v>605</v>
+      </c>
+      <c r="R82" s="19" t="s">
+        <v>630</v>
       </c>
       <c r="S82" s="13">
-        <v>45513</v>
+        <v>45118</v>
       </c>
       <c r="T82" s="13">
-        <v>46607</v>
+        <v>46213</v>
       </c>
       <c r="U82" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="83" spans="1:23">
       <c r="A83" s="3" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H83" s="14" t="s">
-        <v>651</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>545</v>
+        <v>16</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>662</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O83" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R83" s="17" t="s">
-        <v>642</v>
+        <v>605</v>
+      </c>
+      <c r="R83" s="19" t="s">
+        <v>630</v>
       </c>
       <c r="S83" s="13">
-        <v>44664</v>
+        <v>45099</v>
       </c>
       <c r="T83" s="13">
-        <v>45759</v>
+        <v>46194</v>
       </c>
       <c r="U83" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="84" spans="1:23">
       <c r="A84" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>569</v>
+        <v>468</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>306</v>
+        <v>15</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>403</v>
+        <v>330</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>568</v>
+        <v>265</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>550</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O84"/>
+      <c r="O84" t="s">
+        <v>180</v>
+      </c>
+      <c r="P84" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q84" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R84" s="17" t="s">
+        <v>628</v>
+      </c>
       <c r="S84" s="13">
-        <v>45757</v>
+        <v>44664</v>
       </c>
       <c r="T84" s="13">
-        <v>46852</v>
+        <v>45759</v>
       </c>
       <c r="U84" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:23">
+      <c r="A85" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="B85" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>570</v>
+        <v>467</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>133</v>
@@ -7536,153 +7484,175 @@
         <v>15</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>405</v>
+        <v>352</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="J85" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O85" t="s">
+        <v>179</v>
+      </c>
+      <c r="P85" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q85" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R85" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="S85" s="13">
+        <v>45012</v>
+      </c>
+      <c r="T85" s="13">
+        <v>46107</v>
+      </c>
+      <c r="U85" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23">
+      <c r="A86" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J86" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="L85" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="N85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O85"/>
-      <c r="R85" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="S85" s="13">
-        <v>44425</v>
-      </c>
-      <c r="T85" s="13">
-        <v>45520</v>
-      </c>
-      <c r="U85" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="86" spans="1:23">
-      <c r="B86" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="J86" s="9" t="s">
-        <v>581</v>
-      </c>
       <c r="L86" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O86" t="s">
-        <v>199</v>
-      </c>
-      <c r="R86" s="17" t="s">
-        <v>644</v>
+        <v>197</v>
+      </c>
+      <c r="P86" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q86" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R86" s="15" t="s">
+        <v>645</v>
       </c>
       <c r="S86" s="13">
-        <v>45265</v>
+        <v>45264</v>
       </c>
       <c r="T86" s="13">
-        <v>46360</v>
+        <v>46359</v>
       </c>
       <c r="U86" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="87" spans="1:23">
       <c r="A87" s="3" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O87" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R87" s="17" t="s">
         <v>645</v>
       </c>
       <c r="S87" s="13">
-        <v>45848</v>
+        <v>45264</v>
       </c>
       <c r="T87" s="13">
-        <v>46943</v>
+        <v>46389</v>
       </c>
       <c r="U87" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="88" spans="1:23">
+      <c r="A88" s="3" t="s">
+        <v>412</v>
+      </c>
       <c r="B88" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C88" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>484</v>
+      </c>
       <c r="D88" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>133</v>
@@ -7691,410 +7661,371 @@
         <v>15</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="J88" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O88" t="s">
+        <v>590</v>
+      </c>
+      <c r="P88" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q88" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R88" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="S88" s="13">
+        <v>45265</v>
+      </c>
+      <c r="T88" s="13">
+        <v>46360</v>
+      </c>
+      <c r="U88" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23">
+      <c r="A89" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J89" s="3"/>
+      <c r="L89" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P89" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="L88" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O88" t="s">
-        <v>172</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q88" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R88" s="17" t="s">
-        <v>652</v>
-      </c>
-      <c r="S88" s="13">
-        <v>45654</v>
-      </c>
-      <c r="T88" s="13">
-        <v>46748</v>
-      </c>
-      <c r="U88" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23">
-      <c r="B89" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O89" t="s">
-        <v>605</v>
-      </c>
-      <c r="P89" s="11" t="s">
-        <v>617</v>
-      </c>
       <c r="Q89" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="R89" s="16" t="s">
+        <v>624</v>
+      </c>
+      <c r="S89" s="13">
+        <v>44829</v>
+      </c>
+      <c r="T89" s="13">
+        <v>45194</v>
+      </c>
+      <c r="U89" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="R89" s="17" t="s">
-        <v>644</v>
-      </c>
-      <c r="S89" s="13">
-        <v>45419</v>
-      </c>
-      <c r="T89" s="13">
-        <v>46513</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>628</v>
-      </c>
       <c r="W89" s="8"/>
     </row>
     <row r="90" spans="1:23">
+      <c r="A90" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="B90" s="3" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>490</v>
+        <v>25</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>603</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J90" s="3"/>
       <c r="L90" s="3" t="s">
-        <v>321</v>
+        <v>656</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>321</v>
+        <v>27</v>
       </c>
       <c r="N90" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O90" t="s">
-        <v>205</v>
-      </c>
       <c r="P90" s="3" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R90" s="17" t="s">
-        <v>660</v>
+        <v>624</v>
       </c>
       <c r="S90" s="13">
-        <v>44697</v>
+        <v>45563</v>
       </c>
       <c r="T90" s="13">
-        <v>45792</v>
+        <v>45563</v>
       </c>
       <c r="U90" s="3" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
     </row>
     <row r="91" spans="1:23">
+      <c r="A91" s="3" t="s">
+        <v>336</v>
+      </c>
       <c r="B91" s="3" t="s">
-        <v>126</v>
+        <v>44</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>491</v>
+        <v>434</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>602</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="J91" s="3"/>
       <c r="L91" s="3" t="s">
-        <v>321</v>
+        <v>496</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>321</v>
+        <v>27</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O91" t="s">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R91" s="17" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="S91" s="13">
-        <v>44705</v>
+        <v>45895</v>
       </c>
       <c r="T91" s="13">
-        <v>45800</v>
+        <v>46990</v>
       </c>
       <c r="U91" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="92" spans="1:23">
       <c r="B92" s="3" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>590</v>
+        <v>435</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>305</v>
+        <v>15</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>620</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J92" s="3"/>
       <c r="L92" s="3" t="s">
-        <v>321</v>
+        <v>496</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>321</v>
+        <v>27</v>
       </c>
       <c r="N92" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O92" t="s">
-        <v>208</v>
+      <c r="O92" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="Q92" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="U92" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23">
+      <c r="B93" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="J93" s="3"/>
+      <c r="L93" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O93" t="s">
+        <v>200</v>
+      </c>
+      <c r="R93" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="S93" s="13">
+        <v>45897</v>
+      </c>
+      <c r="T93" s="13">
+        <v>46992</v>
+      </c>
+      <c r="U93" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23">
+      <c r="B94" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J94" s="3"/>
+      <c r="L94" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O94"/>
+      <c r="U94" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="S92" s="13">
-        <v>43427</v>
-      </c>
-      <c r="T92" s="13">
-        <v>45272</v>
-      </c>
-      <c r="U92" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23">
-      <c r="A93" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="J93" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="N93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O93" t="s">
-        <v>179</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q93" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R93" s="17" t="s">
-        <v>642</v>
-      </c>
-      <c r="S93" s="13">
-        <v>45012</v>
-      </c>
-      <c r="T93" s="13">
-        <v>46107</v>
-      </c>
-      <c r="U93" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23">
-      <c r="A94" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O94" t="s">
-        <v>600</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R94" s="17" t="s">
-        <v>658</v>
-      </c>
-      <c r="S94" s="13">
-        <v>45265</v>
-      </c>
-      <c r="T94" s="13">
-        <v>46360</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="95" spans="1:23">
+      <c r="A95" s="3" t="s">
+        <v>399</v>
+      </c>
       <c r="B95" s="3" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>345</v>
+        <v>16</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>515</v>
+        <v>274</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>559</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="M95" s="3" t="s">
         <v>312</v>
@@ -8103,57 +8034,57 @@
         <v>20</v>
       </c>
       <c r="O95" t="s">
-        <v>594</v>
+        <v>189</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R95" s="17" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="S95" s="13">
-        <v>45502</v>
+        <v>45539</v>
       </c>
       <c r="T95" s="13">
-        <v>46596</v>
+        <v>46633</v>
       </c>
       <c r="U95" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="96" spans="1:23">
       <c r="A96" s="3" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>371</v>
+        <v>16</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>547</v>
+        <v>275</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>560</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>312</v>
@@ -8162,57 +8093,57 @@
         <v>20</v>
       </c>
       <c r="O96" t="s">
-        <v>597</v>
+        <v>190</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R96" s="17" t="s">
-        <v>649</v>
+        <v>625</v>
       </c>
       <c r="S96" s="13">
-        <v>45024</v>
+        <v>45547</v>
       </c>
       <c r="T96" s="13">
-        <v>46119</v>
+        <v>46641</v>
       </c>
       <c r="U96" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="97" spans="1:24">
       <c r="A97" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>371</v>
+        <v>16</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="J97" s="9" t="s">
-        <v>566</v>
+        <v>293</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>575</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="M97" s="3" t="s">
         <v>312</v>
@@ -8221,39 +8152,36 @@
         <v>20</v>
       </c>
       <c r="O97" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="R97" s="17" t="s">
-        <v>649</v>
+        <v>625</v>
       </c>
       <c r="S97" s="13">
-        <v>44980</v>
+        <v>45498</v>
       </c>
       <c r="T97" s="13">
-        <v>46075</v>
+        <v>46592</v>
       </c>
       <c r="U97" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="98" spans="1:24">
-      <c r="A98" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="B98" s="3" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>211</v>
+        <v>441</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>133</v>
@@ -8265,13 +8193,13 @@
         <v>345</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>578</v>
+        <v>515</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>211</v>
+        <v>312</v>
       </c>
       <c r="M98" s="3" t="s">
         <v>312</v>
@@ -8280,36 +8208,39 @@
         <v>20</v>
       </c>
       <c r="O98" t="s">
-        <v>196</v>
+        <v>584</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="R98" s="15" t="s">
-        <v>639</v>
+        <v>605</v>
+      </c>
+      <c r="R98" s="17" t="s">
+        <v>629</v>
       </c>
       <c r="S98" s="13">
-        <v>45517</v>
+        <v>45502</v>
       </c>
       <c r="T98" s="13">
-        <v>46611</v>
+        <v>46596</v>
       </c>
       <c r="U98" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="99" spans="1:24">
+      <c r="A99" s="3" t="s">
+        <v>381</v>
+      </c>
       <c r="B99" s="3" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>133</v>
@@ -8318,13 +8249,13 @@
         <v>15</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>312</v>
@@ -8336,155 +8267,199 @@
         <v>20</v>
       </c>
       <c r="O99" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="R99" s="17" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="S99" s="13">
-        <v>44694</v>
+        <v>45024</v>
       </c>
       <c r="T99" s="13">
-        <v>45789</v>
+        <v>46119</v>
       </c>
       <c r="U99" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="100" spans="1:24">
+      <c r="A100" s="3" t="s">
+        <v>401</v>
+      </c>
       <c r="B100" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J100" s="3"/>
+        <v>371</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>561</v>
+      </c>
       <c r="L100" s="3" t="s">
-        <v>496</v>
+        <v>325</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>27</v>
+        <v>312</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>37</v>
+      <c r="O100" t="s">
+        <v>191</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>619</v>
+        <v>605</v>
+      </c>
+      <c r="R100" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="S100" s="13">
+        <v>44980</v>
+      </c>
+      <c r="T100" s="13">
+        <v>46075</v>
       </c>
       <c r="U100" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="101" spans="1:24">
+      <c r="A101" s="3" t="s">
+        <v>408</v>
+      </c>
       <c r="B101" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>485</v>
+        <v>211</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>16</v>
+        <v>345</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="J101" s="3"/>
+        <v>285</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>570</v>
+      </c>
       <c r="L101" s="3" t="s">
-        <v>496</v>
+        <v>211</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>27</v>
+        <v>312</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O101" t="s">
-        <v>200</v>
-      </c>
-      <c r="R101" s="17" t="s">
-        <v>659</v>
+        <v>196</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R101" s="15" t="s">
+        <v>629</v>
       </c>
       <c r="S101" s="13">
-        <v>45897</v>
+        <v>45517</v>
       </c>
       <c r="T101" s="13">
-        <v>46992</v>
+        <v>46611</v>
       </c>
       <c r="U101" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="102" spans="1:24">
       <c r="B102" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>307</v>
+        <v>15</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>419</v>
+        <v>352</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J102" s="3"/>
+        <v>294</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>576</v>
+      </c>
       <c r="L102" s="3" t="s">
-        <v>496</v>
+        <v>312</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>27</v>
+        <v>312</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O102"/>
+      <c r="O102" t="s">
+        <v>591</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R102" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="S102" s="13">
+        <v>44694</v>
+      </c>
+      <c r="T102" s="13">
+        <v>45789</v>
+      </c>
       <c r="U102" s="3" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
     </row>
     <row r="103" spans="1:24">

--- a/src/assets/EQUIPOS.xlsx
+++ b/src/assets/EQUIPOS.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A94719-7F59-4FC5-97BB-A8FBB483E3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6BB03A-CA94-4C94-A43F-E60A1CC30B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="664">
   <si>
     <t>Etiqueta</t>
   </si>
@@ -941,9 +941,6 @@
     <t>IBM</t>
   </si>
   <si>
-    <t>Gigabyte</t>
-  </si>
-  <si>
     <t>Ama de llaves</t>
   </si>
   <si>
@@ -1520,9 +1517,6 @@
     <t>ARRIVA\jefalmcun</t>
   </si>
   <si>
-    <t>CROWNCUN\amadellaves2</t>
-  </si>
-  <si>
     <t>Room Service</t>
   </si>
   <si>
@@ -1544,9 +1538,6 @@
     <t>Subchef</t>
   </si>
   <si>
-    <t>LOCAL\nitro</t>
-  </si>
-  <si>
     <t>Teatro Yumik</t>
   </si>
   <si>
@@ -1574,9 +1565,6 @@
     <t>Laptop para capacitacon</t>
   </si>
   <si>
-    <t>CRONCUN\capacitacion</t>
-  </si>
-  <si>
     <t>ARRIVA\gtechcun</t>
   </si>
   <si>
@@ -1667,12 +1655,6 @@
     <t>ARRIVA\gtemantocun</t>
   </si>
   <si>
-    <t>CROWNCUN\jefemanto</t>
-  </si>
-  <si>
-    <t>CROWNCUN\nominas</t>
-  </si>
-  <si>
     <t>ARRIVA\frontcun01</t>
   </si>
   <si>
@@ -1715,9 +1697,6 @@
     <t>Monitor Elevadores</t>
   </si>
   <si>
-    <t>CROWNCUN\monitoreo</t>
-  </si>
-  <si>
     <t>Monitor Camaras 2</t>
   </si>
   <si>
@@ -1812,9 +1791,6 @@
   </si>
   <si>
     <t>ARRIVA\gscun11</t>
-  </si>
-  <si>
-    <t>LOCAL\vlo</t>
   </si>
   <si>
     <t>Version Office</t>
@@ -2034,6 +2010,27 @@
   </si>
   <si>
     <t>ARRIVA\asiscapcun</t>
+  </si>
+  <si>
+    <t>ARRIVA\capacun01</t>
+  </si>
+  <si>
+    <t>ARRIVA\nominascun</t>
+  </si>
+  <si>
+    <t>ARRIVA\amallavescun01</t>
+  </si>
+  <si>
+    <t>ARRIVA\monitoreocun</t>
+  </si>
+  <si>
+    <t>ARRIVA\jefemantocun</t>
+  </si>
+  <si>
+    <t>ARRIVA\spacun01</t>
+  </si>
+  <si>
+    <t>3CHB9M2</t>
   </si>
 </sst>
 </file>
@@ -2726,10 +2723,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>426</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -2747,7 +2744,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>7</v>
@@ -2765,36 +2762,36 @@
         <v>11</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>14</v>
@@ -2809,13 +2806,13 @@
         <v>219</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>20</v>
@@ -2824,13 +2821,13 @@
         <v>141</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S2" s="13">
         <v>45513</v>
@@ -2839,21 +2836,21 @@
         <v>46607</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>14</v>
@@ -2862,19 +2859,19 @@
         <v>15</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>220</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>20</v>
@@ -2883,13 +2880,13 @@
         <v>142</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="S3" s="13">
         <v>44781</v>
@@ -2898,7 +2895,7 @@
         <v>45876</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -2906,10 +2903,10 @@
         <v>47</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>14</v>
@@ -2918,20 +2915,20 @@
         <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>221</v>
       </c>
       <c r="I4" s="21"/>
       <c r="J4" s="3" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>20</v>
@@ -2940,13 +2937,13 @@
         <v>143</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S4" s="13">
         <v>44772</v>
@@ -2955,21 +2952,21 @@
         <v>45867</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>14</v>
@@ -2978,19 +2975,19 @@
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>223</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>20</v>
@@ -2999,13 +2996,13 @@
         <v>145</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="S5" s="13">
         <v>44441</v>
@@ -3014,7 +3011,7 @@
         <v>45537</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -3022,10 +3019,10 @@
         <v>50</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>14</v>
@@ -3040,13 +3037,13 @@
         <v>224</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>20</v>
@@ -3055,13 +3052,13 @@
         <v>146</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S6" s="13">
         <v>45468</v>
@@ -3070,21 +3067,21 @@
         <v>46562</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>133</v>
@@ -3093,19 +3090,19 @@
         <v>15</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>222</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>20</v>
@@ -3114,13 +3111,13 @@
         <v>144</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="S7" s="13">
         <v>45516</v>
@@ -3129,21 +3126,21 @@
         <v>46610</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>14</v>
@@ -3152,19 +3149,17 @@
         <v>305</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>509</v>
-      </c>
+      <c r="J8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>20</v>
@@ -3177,21 +3172,21 @@
         <v>46149</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>14</v>
@@ -3206,13 +3201,13 @@
         <v>226</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>20</v>
@@ -3221,13 +3216,13 @@
         <v>147</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S9" s="13">
         <v>45119</v>
@@ -3236,21 +3231,21 @@
         <v>46214</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>14</v>
@@ -3265,13 +3260,13 @@
         <v>228</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>20</v>
@@ -3280,13 +3275,13 @@
         <v>149</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S10" s="13">
         <v>45016</v>
@@ -3295,21 +3290,21 @@
         <v>46111</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>133</v>
@@ -3318,19 +3313,19 @@
         <v>15</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>227</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>20</v>
@@ -3339,13 +3334,13 @@
         <v>148</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="S11" s="13">
         <v>45026</v>
@@ -3354,7 +3349,7 @@
         <v>46121</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -3362,10 +3357,10 @@
         <v>55</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>133</v>
@@ -3374,19 +3369,19 @@
         <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>229</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>20</v>
@@ -3395,13 +3390,13 @@
         <v>150</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="S12" s="13">
         <v>44716</v>
@@ -3410,21 +3405,21 @@
         <v>45811</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>14</v>
@@ -3433,19 +3428,19 @@
         <v>15</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>232</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>20</v>
@@ -3454,7 +3449,7 @@
         <v>152</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S13" s="13">
         <v>44707</v>
@@ -3463,21 +3458,21 @@
         <v>45802</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>14</v>
@@ -3492,13 +3487,13 @@
         <v>233</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>20</v>
@@ -3507,13 +3502,13 @@
         <v>153</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S14" s="13">
         <v>45012</v>
@@ -3522,21 +3517,21 @@
         <v>46107</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>14</v>
@@ -3545,19 +3540,19 @@
         <v>15</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>237</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>20</v>
@@ -3566,13 +3561,13 @@
         <v>155</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="S15" s="13">
         <v>44833</v>
@@ -3581,21 +3576,21 @@
         <v>45928</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>133</v>
@@ -3604,19 +3599,19 @@
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>234</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>20</v>
@@ -3625,13 +3620,13 @@
         <v>154</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="S16" s="13">
         <v>44667</v>
@@ -3640,21 +3635,21 @@
         <v>45762</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>133</v>
@@ -3663,32 +3658,32 @@
         <v>15</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>235</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>519</v>
+        <v>657</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O17"/>
       <c r="P17" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="S17" s="13">
         <v>45517</v>
@@ -3697,21 +3692,21 @@
         <v>46611</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>133</v>
@@ -3720,34 +3715,34 @@
         <v>15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>236</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O18" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="S18" s="13">
         <v>45873</v>
@@ -3756,7 +3751,7 @@
         <v>46968</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -3767,10 +3762,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>14</v>
@@ -3785,7 +3780,7 @@
         <v>17</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>18</v>
@@ -3800,13 +3795,13 @@
         <v>21</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R19" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S19" s="13">
         <v>45498</v>
@@ -3815,21 +3810,21 @@
         <v>46595</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>14</v>
@@ -3838,13 +3833,13 @@
         <v>15</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>212</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>18</v>
@@ -3859,13 +3854,13 @@
         <v>134</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R20" s="17" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="S20" s="13">
         <v>44442</v>
@@ -3874,21 +3869,21 @@
         <v>45537</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>14</v>
@@ -3903,7 +3898,7 @@
         <v>213</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>18</v>
@@ -3918,13 +3913,13 @@
         <v>135</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R21" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S21" s="13">
         <v>45498</v>
@@ -3933,21 +3928,21 @@
         <v>46592</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>14</v>
@@ -3956,16 +3951,16 @@
         <v>15</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>243</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>19</v>
@@ -3977,13 +3972,13 @@
         <v>161</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="S22" s="13">
         <v>44439</v>
@@ -3992,21 +3987,21 @@
         <v>45534</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>14</v>
@@ -4021,10 +4016,10 @@
         <v>244</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>19</v>
@@ -4036,13 +4031,13 @@
         <v>162</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R23" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S23" s="13">
         <v>45020</v>
@@ -4051,21 +4046,21 @@
         <v>46115</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>14</v>
@@ -4080,10 +4075,10 @@
         <v>245</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>19</v>
@@ -4095,13 +4090,13 @@
         <v>163</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S24" s="13">
         <v>45020</v>
@@ -4110,21 +4105,21 @@
         <v>46115</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>14</v>
@@ -4133,16 +4128,16 @@
         <v>15</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>247</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>19</v>
@@ -4154,13 +4149,13 @@
         <v>164</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R25" s="17" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S25" s="13">
         <v>44701</v>
@@ -4169,7 +4164,7 @@
         <v>45796</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -4177,10 +4172,10 @@
         <v>74</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>14</v>
@@ -4189,16 +4184,16 @@
         <v>15</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>248</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>19</v>
@@ -4210,13 +4205,13 @@
         <v>165</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R26" s="17" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S26" s="13">
         <v>44657</v>
@@ -4225,19 +4220,19 @@
         <v>45752</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>14</v>
@@ -4246,14 +4241,14 @@
         <v>15</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>249</v>
       </c>
       <c r="J27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>19</v>
@@ -4263,7 +4258,7 @@
       </c>
       <c r="O27"/>
       <c r="R27" s="17" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="S27" s="13">
         <v>43580</v>
@@ -4272,21 +4267,21 @@
         <v>44700</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>14</v>
@@ -4295,16 +4290,16 @@
         <v>15</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>252</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>19</v>
@@ -4316,13 +4311,13 @@
         <v>167</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R28" s="17" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="S28" s="13">
         <v>45849</v>
@@ -4331,19 +4326,19 @@
         <v>46944</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>14</v>
@@ -4352,16 +4347,16 @@
         <v>15</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>253</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>19</v>
@@ -4373,13 +4368,13 @@
         <v>168</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R29" s="17" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="S29" s="13">
         <v>44446</v>
@@ -4388,21 +4383,21 @@
         <v>45541</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>14</v>
@@ -4417,10 +4412,10 @@
         <v>254</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>19</v>
@@ -4432,13 +4427,13 @@
         <v>169</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R30" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S30" s="13">
         <v>45012</v>
@@ -4447,21 +4442,21 @@
         <v>46107</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>85</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>14</v>
@@ -4470,16 +4465,16 @@
         <v>15</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>258</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>19</v>
@@ -4491,13 +4486,13 @@
         <v>173</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S31" s="13">
         <v>44664</v>
@@ -4506,21 +4501,21 @@
         <v>45759</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>14</v>
@@ -4535,10 +4530,10 @@
         <v>259</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>19</v>
@@ -4550,13 +4545,13 @@
         <v>174</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R32" s="19" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S32" s="13">
         <v>45386</v>
@@ -4565,21 +4560,21 @@
         <v>46115</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>14</v>
@@ -4588,19 +4583,19 @@
         <v>15</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>266</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>551</v>
+        <v>658</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>19</v>
+        <v>313</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>20</v>
@@ -4609,13 +4604,13 @@
         <v>181</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R33" s="17" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="S33" s="13">
         <v>44377</v>
@@ -4624,7 +4619,7 @@
         <v>45472</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -4632,10 +4627,10 @@
         <v>110</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>14</v>
@@ -4644,13 +4639,13 @@
         <v>15</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>282</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>26</v>
@@ -4665,13 +4660,13 @@
         <v>195</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R34" s="15" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="S34" s="13">
         <v>45894</v>
@@ -4680,16 +4675,16 @@
         <v>46989</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35" spans="1:21">
       <c r="B35" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>133</v>
@@ -4698,14 +4693,14 @@
         <v>305</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>19</v>
@@ -4714,13 +4709,13 @@
         <v>20</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="S35" s="13">
         <v>43526</v>
@@ -4729,21 +4724,21 @@
         <v>44641</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>133</v>
@@ -4752,16 +4747,16 @@
         <v>15</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>231</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>19</v>
@@ -4773,13 +4768,13 @@
         <v>151</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R36" s="17" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="S36" s="13">
         <v>45762</v>
@@ -4788,7 +4783,7 @@
         <v>46857</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -4796,10 +4791,10 @@
         <v>72</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>133</v>
@@ -4808,16 +4803,16 @@
         <v>15</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>246</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>19</v>
@@ -4827,13 +4822,13 @@
       </c>
       <c r="O37"/>
       <c r="P37" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R37" s="17" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="S37" s="13">
         <v>45058</v>
@@ -4842,21 +4837,21 @@
         <v>46153</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>133</v>
@@ -4865,16 +4860,16 @@
         <v>15</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>19</v>
@@ -4883,16 +4878,16 @@
         <v>20</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R38" s="17" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="S38" s="13">
         <v>45514</v>
@@ -4901,21 +4896,21 @@
         <v>46608</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>133</v>
@@ -4924,13 +4919,13 @@
         <v>15</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>250</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>210</v>
@@ -4942,16 +4937,16 @@
         <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R39" s="17" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="S39" s="13">
         <v>45856</v>
@@ -4960,21 +4955,21 @@
         <v>46951</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>133</v>
@@ -4983,16 +4978,16 @@
         <v>15</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>251</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>19</v>
@@ -5004,13 +4999,13 @@
         <v>166</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R40" s="17" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="S40" s="13">
         <v>45518</v>
@@ -5019,7 +5014,7 @@
         <v>46612</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -5027,10 +5022,10 @@
         <v>111</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>133</v>
@@ -5039,13 +5034,13 @@
         <v>15</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>283</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>26</v>
@@ -5058,36 +5053,36 @@
       </c>
       <c r="O41"/>
       <c r="P41" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="S41" s="13">
         <v>43755</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>133</v>
@@ -5096,13 +5091,13 @@
         <v>15</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>284</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>26</v>
@@ -5114,16 +5109,16 @@
         <v>20</v>
       </c>
       <c r="O42" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R42" s="15" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="S42" s="13">
         <v>45513</v>
@@ -5132,21 +5127,21 @@
         <v>46607</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>14</v>
@@ -5161,13 +5156,13 @@
         <v>214</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>20</v>
@@ -5176,13 +5171,13 @@
         <v>136</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R43" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S43" s="13">
         <v>45498</v>
@@ -5191,7 +5186,7 @@
         <v>46592</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -5199,10 +5194,10 @@
         <v>41</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>14</v>
@@ -5217,13 +5212,13 @@
         <v>215</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>501</v>
+        <v>659</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>20</v>
@@ -5232,13 +5227,13 @@
         <v>137</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R44" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S44" s="13">
         <v>45498</v>
@@ -5247,21 +5242,21 @@
         <v>46592</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>14</v>
@@ -5276,13 +5271,13 @@
         <v>216</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>20</v>
@@ -5291,13 +5286,13 @@
         <v>138</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R45" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S45" s="13">
         <v>45519</v>
@@ -5306,21 +5301,21 @@
         <v>46613</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>14</v>
@@ -5329,19 +5324,19 @@
         <v>15</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>217</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>20</v>
@@ -5350,13 +5345,13 @@
         <v>139</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R46" s="17" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="S46" s="13">
         <v>45849</v>
@@ -5365,21 +5360,21 @@
         <v>46944</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>14</v>
@@ -5394,13 +5389,13 @@
         <v>238</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>20</v>
@@ -5409,13 +5404,13 @@
         <v>156</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R47" s="18" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="S47" s="13">
         <v>45021</v>
@@ -5424,21 +5419,21 @@
         <v>46116</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>14</v>
@@ -5447,19 +5442,19 @@
         <v>15</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>239</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>20</v>
@@ -5468,13 +5463,13 @@
         <v>157</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R48" s="17" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="S48" s="13">
         <v>45883</v>
@@ -5483,7 +5478,7 @@
         <v>46978</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -5491,10 +5486,10 @@
         <v>66</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>14</v>
@@ -5503,19 +5498,19 @@
         <v>15</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>240</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>20</v>
@@ -5524,13 +5519,13 @@
         <v>158</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R49" s="17" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="S49" s="13">
         <v>44453</v>
@@ -5539,21 +5534,21 @@
         <v>44817</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>14</v>
@@ -5562,19 +5557,19 @@
         <v>15</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>241</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>20</v>
@@ -5583,13 +5578,13 @@
         <v>159</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R50" s="17" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="S50" s="13">
         <v>43605</v>
@@ -5598,21 +5593,21 @@
         <v>44700</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>14</v>
@@ -5627,13 +5622,13 @@
         <v>242</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>20</v>
@@ -5642,13 +5637,13 @@
         <v>160</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R51" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S51" s="13">
         <v>45099</v>
@@ -5657,21 +5652,21 @@
         <v>46194</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>14</v>
@@ -5680,19 +5675,19 @@
         <v>15</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>260</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>20</v>
@@ -5701,13 +5696,13 @@
         <v>175</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R52" s="17" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="S52" s="13">
         <v>44183</v>
@@ -5716,21 +5711,21 @@
         <v>45277</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>14</v>
@@ -5739,19 +5734,19 @@
         <v>15</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>267</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>20</v>
@@ -5760,13 +5755,13 @@
         <v>182</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R53" s="17" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="S53" s="13">
         <v>44189</v>
@@ -5775,21 +5770,21 @@
         <v>45283</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>14</v>
@@ -5798,19 +5793,19 @@
         <v>15</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>268</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>20</v>
@@ -5819,13 +5814,13 @@
         <v>183</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R54" s="18" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="S54" s="13">
         <v>45849</v>
@@ -5834,21 +5829,21 @@
         <v>46944</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>14</v>
@@ -5863,13 +5858,13 @@
         <v>269</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N55" s="3" t="s">
         <v>20</v>
@@ -5878,13 +5873,13 @@
         <v>184</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R55" s="17" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="S55" s="13">
         <v>45958</v>
@@ -5893,21 +5888,21 @@
         <v>47053</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>14</v>
@@ -5916,19 +5911,19 @@
         <v>15</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>270</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>20</v>
@@ -5937,13 +5932,13 @@
         <v>185</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R56" s="17" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="S56" s="13">
         <v>43580</v>
@@ -5952,21 +5947,21 @@
         <v>44700</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>14</v>
@@ -5975,19 +5970,19 @@
         <v>15</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>271</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>20</v>
@@ -5996,13 +5991,13 @@
         <v>186</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R57" s="17" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="S57" s="13">
         <v>45849</v>
@@ -6011,21 +6006,21 @@
         <v>46944</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>14</v>
@@ -6040,13 +6035,13 @@
         <v>272</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>20</v>
@@ -6055,13 +6050,13 @@
         <v>187</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R58" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S58" s="13">
         <v>45012</v>
@@ -6070,21 +6065,21 @@
         <v>46107</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>14</v>
@@ -6099,13 +6094,13 @@
         <v>273</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>20</v>
@@ -6114,13 +6109,13 @@
         <v>188</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R59" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S59" s="13">
         <v>45537</v>
@@ -6129,7 +6124,7 @@
         <v>46631</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -6137,10 +6132,10 @@
         <v>104</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>14</v>
@@ -6149,17 +6144,17 @@
         <v>305</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>277</v>
       </c>
       <c r="J60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>20</v>
@@ -6168,10 +6163,10 @@
         <v>192</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="S60" s="13">
         <v>45146</v>
@@ -6180,7 +6175,7 @@
         <v>46256</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -6188,26 +6183,31 @@
         <v>107</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="H61" s="1"/>
+        <v>305</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>663</v>
+      </c>
       <c r="J61" s="3" t="s">
-        <v>566</v>
+        <v>660</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>20</v>
@@ -6215,8 +6215,14 @@
       <c r="O61" t="s">
         <v>193</v>
       </c>
+      <c r="S61" s="13">
+        <v>43108</v>
+      </c>
+      <c r="T61" s="13">
+        <v>43564</v>
+      </c>
       <c r="U61" s="3" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -6224,10 +6230,10 @@
         <v>108</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>14</v>
@@ -6236,17 +6242,17 @@
         <v>305</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>280</v>
       </c>
       <c r="J62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>20</v>
@@ -6261,7 +6267,7 @@
         <v>46607</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -6269,10 +6275,10 @@
         <v>109</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>14</v>
@@ -6281,34 +6287,34 @@
         <v>15</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>281</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O63" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R63" s="15" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S63" s="13">
         <v>44699</v>
@@ -6317,21 +6323,21 @@
         <v>45794</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>119</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>14</v>
@@ -6340,19 +6346,19 @@
         <v>15</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>291</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>20</v>
@@ -6361,13 +6367,13 @@
         <v>201</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R64" s="17" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="S64" s="13">
         <v>43580</v>
@@ -6376,21 +6382,21 @@
         <v>44700</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>14</v>
@@ -6399,19 +6405,19 @@
         <v>305</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>292</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>20</v>
@@ -6420,10 +6426,10 @@
         <v>202</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="S65" s="13">
         <v>43108</v>
@@ -6432,21 +6438,21 @@
         <v>43564</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>133</v>
@@ -6455,19 +6461,19 @@
         <v>15</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>20</v>
@@ -6476,13 +6482,13 @@
         <v>170</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R66" s="17" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="S66" s="13">
         <v>44664</v>
@@ -6491,21 +6497,21 @@
         <v>45759</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>105</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>133</v>
@@ -6514,17 +6520,17 @@
         <v>306</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>20</v>
@@ -6537,7 +6543,7 @@
         <v>46852</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -6545,10 +6551,10 @@
         <v>106</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>133</v>
@@ -6557,24 +6563,24 @@
         <v>15</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>279</v>
       </c>
       <c r="J68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O68"/>
       <c r="R68" s="1" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="S68" s="13">
         <v>44425</v>
@@ -6583,7 +6589,7 @@
         <v>45520</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -6591,10 +6597,10 @@
         <v>116</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>133</v>
@@ -6603,19 +6609,19 @@
         <v>15</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>288</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>20</v>
@@ -6624,7 +6630,7 @@
         <v>199</v>
       </c>
       <c r="R69" s="17" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="S69" s="13">
         <v>45265</v>
@@ -6633,21 +6639,21 @@
         <v>46360</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>133</v>
@@ -6656,19 +6662,19 @@
         <v>15</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>255</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>20</v>
@@ -6677,13 +6683,13 @@
         <v>171</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R70" s="17" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="S70" s="13">
         <v>45848</v>
@@ -6692,7 +6698,7 @@
         <v>46943</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -6700,10 +6706,10 @@
         <v>124</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>14</v>
@@ -6718,13 +6724,13 @@
         <v>296</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>20</v>
@@ -6733,13 +6739,13 @@
         <v>204</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R71" s="17" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S71" s="13">
         <v>45112</v>
@@ -6748,7 +6754,7 @@
         <v>46207</v>
       </c>
       <c r="U71" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="72" spans="1:21">
@@ -6756,10 +6762,10 @@
         <v>127</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>14</v>
@@ -6768,30 +6774,30 @@
         <v>15</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>299</v>
       </c>
       <c r="J72" s="3"/>
       <c r="L72" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O72"/>
       <c r="P72" s="3" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R72" s="17" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S72" s="13">
         <v>44697</v>
@@ -6800,7 +6806,7 @@
         <v>45792</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="73" spans="1:21">
@@ -6808,10 +6814,10 @@
         <v>128</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>14</v>
@@ -6826,13 +6832,13 @@
         <v>300</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>20</v>
@@ -6841,13 +6847,13 @@
         <v>207</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R73" s="17" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="S73" s="13">
         <v>45349</v>
@@ -6856,7 +6862,7 @@
         <v>46444</v>
       </c>
       <c r="U73" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="74" spans="1:21">
@@ -6864,10 +6870,10 @@
         <v>129</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>14</v>
@@ -6876,19 +6882,17 @@
         <v>305</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J74" s="3" t="s">
-        <v>599</v>
-      </c>
+      <c r="J74" s="3"/>
       <c r="L74" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>20</v>
@@ -6901,7 +6905,7 @@
         <v>43598</v>
       </c>
       <c r="U74" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="75" spans="1:21">
@@ -6909,10 +6913,10 @@
         <v>131</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>14</v>
@@ -6921,17 +6925,17 @@
         <v>305</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>303</v>
       </c>
       <c r="J75" s="3"/>
       <c r="L75" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>20</v>
@@ -6940,10 +6944,10 @@
         <v>209</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="S75" s="13">
         <v>43066</v>
@@ -6952,7 +6956,7 @@
         <v>43522</v>
       </c>
       <c r="U75" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="76" spans="1:21">
@@ -6961,7 +6965,7 @@
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>133</v>
@@ -6970,19 +6974,19 @@
         <v>15</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>257</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>20</v>
@@ -6991,13 +6995,13 @@
         <v>172</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R76" s="17" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="S76" s="13">
         <v>45654</v>
@@ -7006,7 +7010,7 @@
         <v>46748</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="77" spans="1:21">
@@ -7015,7 +7019,7 @@
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>133</v>
@@ -7024,34 +7028,34 @@
         <v>15</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>295</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O77" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="P77" s="11" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R77" s="17" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="S77" s="13">
         <v>45419</v>
@@ -7060,7 +7064,7 @@
         <v>46513</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="78" spans="1:21">
@@ -7068,10 +7072,10 @@
         <v>125</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>133</v>
@@ -7080,19 +7084,19 @@
         <v>15</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>297</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>20</v>
@@ -7101,13 +7105,13 @@
         <v>205</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R78" s="17" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="S78" s="13">
         <v>44697</v>
@@ -7116,7 +7120,7 @@
         <v>45792</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="79" spans="1:21">
@@ -7124,10 +7128,10 @@
         <v>126</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>133</v>
@@ -7136,19 +7140,19 @@
         <v>15</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>298</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>20</v>
@@ -7157,13 +7161,13 @@
         <v>206</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R79" s="17" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="S79" s="13">
         <v>44705</v>
@@ -7172,7 +7176,7 @@
         <v>45800</v>
       </c>
       <c r="U79" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="80" spans="1:21">
@@ -7180,10 +7184,10 @@
         <v>130</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>133</v>
@@ -7192,19 +7196,19 @@
         <v>305</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>302</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>20</v>
@@ -7213,10 +7217,10 @@
         <v>208</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="S80" s="13">
         <v>43427</v>
@@ -7225,21 +7229,21 @@
         <v>45272</v>
       </c>
       <c r="U80" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="81" spans="1:23">
       <c r="A81" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>14</v>
@@ -7248,19 +7252,19 @@
         <v>15</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>261</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>20</v>
@@ -7269,13 +7273,13 @@
         <v>176</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R81" s="19" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S81" s="13">
         <v>44699</v>
@@ -7284,21 +7288,21 @@
         <v>45794</v>
       </c>
       <c r="U81" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="82" spans="1:23">
       <c r="A82" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>14</v>
@@ -7313,13 +7317,13 @@
         <v>262</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>20</v>
@@ -7328,13 +7332,13 @@
         <v>177</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R82" s="19" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S82" s="13">
         <v>45118</v>
@@ -7343,21 +7347,21 @@
         <v>46213</v>
       </c>
       <c r="U82" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="83" spans="1:23">
       <c r="A83" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>14</v>
@@ -7372,13 +7376,13 @@
         <v>263</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>20</v>
@@ -7387,13 +7391,13 @@
         <v>178</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R83" s="19" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="S83" s="13">
         <v>45099</v>
@@ -7402,21 +7406,21 @@
         <v>46194</v>
       </c>
       <c r="U83" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="84" spans="1:23">
       <c r="A84" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>14</v>
@@ -7425,19 +7429,19 @@
         <v>15</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>265</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>550</v>
+        <v>661</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>20</v>
@@ -7446,13 +7450,13 @@
         <v>180</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R84" s="17" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="S84" s="13">
         <v>44664</v>
@@ -7461,21 +7465,21 @@
         <v>45759</v>
       </c>
       <c r="U84" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="85" spans="1:23">
       <c r="A85" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>133</v>
@@ -7484,19 +7488,19 @@
         <v>15</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>264</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>20</v>
@@ -7505,13 +7509,13 @@
         <v>179</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R85" s="17" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="S85" s="13">
         <v>45012</v>
@@ -7520,21 +7524,21 @@
         <v>46107</v>
       </c>
       <c r="U85" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="86" spans="1:23">
       <c r="A86" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>14</v>
@@ -7543,19 +7547,19 @@
         <v>15</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>286</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>571</v>
+        <v>662</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>20</v>
@@ -7564,13 +7568,13 @@
         <v>197</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R86" s="15" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="S86" s="13">
         <v>45264</v>
@@ -7579,21 +7583,21 @@
         <v>46359</v>
       </c>
       <c r="U86" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="87" spans="1:23">
       <c r="A87" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>14</v>
@@ -7602,19 +7606,19 @@
         <v>15</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>287</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>20</v>
@@ -7623,13 +7627,13 @@
         <v>198</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R87" s="17" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="S87" s="13">
         <v>45264</v>
@@ -7638,21 +7642,21 @@
         <v>46389</v>
       </c>
       <c r="U87" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="88" spans="1:23">
       <c r="A88" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>133</v>
@@ -7661,34 +7665,34 @@
         <v>15</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>289</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N88" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O88" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R88" s="17" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="S88" s="13">
         <v>45265</v>
@@ -7697,7 +7701,7 @@
         <v>46360</v>
       </c>
       <c r="U88" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="89" spans="1:23">
@@ -7711,7 +7715,7 @@
         <v>25</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>23</v>
@@ -7727,7 +7731,7 @@
       </c>
       <c r="J89" s="3"/>
       <c r="L89" s="3" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>27</v>
@@ -7736,13 +7740,13 @@
         <v>20</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R89" s="16" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="S89" s="13">
         <v>44829</v>
@@ -7751,7 +7755,7 @@
         <v>45194</v>
       </c>
       <c r="U89" s="3" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="W89" s="8"/>
     </row>
@@ -7766,7 +7770,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>23</v>
@@ -7782,7 +7786,7 @@
       </c>
       <c r="J90" s="3"/>
       <c r="L90" s="3" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="M90" s="3" t="s">
         <v>27</v>
@@ -7791,13 +7795,13 @@
         <v>20</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R90" s="17" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="S90" s="13">
         <v>45563</v>
@@ -7806,21 +7810,21 @@
         <v>45563</v>
       </c>
       <c r="U90" s="3" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="91" spans="1:23">
       <c r="A91" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>14</v>
@@ -7829,14 +7833,14 @@
         <v>15</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>218</v>
       </c>
       <c r="J91" s="3"/>
       <c r="L91" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>27</v>
@@ -7848,13 +7852,13 @@
         <v>140</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R91" s="17" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="S91" s="13">
         <v>45895</v>
@@ -7863,7 +7867,7 @@
         <v>46990</v>
       </c>
       <c r="U91" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="92" spans="1:23">
@@ -7871,10 +7875,10 @@
         <v>33</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>34</v>
@@ -7890,7 +7894,7 @@
       </c>
       <c r="J92" s="3"/>
       <c r="L92" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>27</v>
@@ -7902,13 +7906,13 @@
         <v>37</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="U92" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="93" spans="1:23">
@@ -7916,10 +7920,10 @@
         <v>118</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>34</v>
@@ -7935,7 +7939,7 @@
       </c>
       <c r="J93" s="3"/>
       <c r="L93" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M93" s="3" t="s">
         <v>27</v>
@@ -7947,7 +7951,7 @@
         <v>200</v>
       </c>
       <c r="R93" s="17" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="S93" s="13">
         <v>45897</v>
@@ -7956,7 +7960,7 @@
         <v>46992</v>
       </c>
       <c r="U93" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="94" spans="1:23">
@@ -7964,10 +7968,10 @@
         <v>132</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>34</v>
@@ -7976,14 +7980,14 @@
         <v>307</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>304</v>
       </c>
       <c r="J94" s="3"/>
       <c r="L94" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>27</v>
@@ -7993,21 +7997,21 @@
       </c>
       <c r="O94"/>
       <c r="U94" s="3" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="95" spans="1:23">
       <c r="A95" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>14</v>
@@ -8022,13 +8026,13 @@
         <v>274</v>
       </c>
       <c r="J95" s="9" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>20</v>
@@ -8037,13 +8041,13 @@
         <v>189</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R95" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S95" s="13">
         <v>45539</v>
@@ -8052,21 +8056,21 @@
         <v>46633</v>
       </c>
       <c r="U95" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="96" spans="1:23">
       <c r="A96" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>14</v>
@@ -8081,13 +8085,13 @@
         <v>275</v>
       </c>
       <c r="J96" s="9" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>20</v>
@@ -8096,13 +8100,13 @@
         <v>190</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R96" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S96" s="13">
         <v>45547</v>
@@ -8111,21 +8115,21 @@
         <v>46641</v>
       </c>
       <c r="U96" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="97" spans="1:24">
       <c r="A97" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>14</v>
@@ -8140,13 +8144,13 @@
         <v>293</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>20</v>
@@ -8155,13 +8159,13 @@
         <v>203</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="R97" s="17" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="S97" s="13">
         <v>45498</v>
@@ -8170,7 +8174,7 @@
         <v>46592</v>
       </c>
       <c r="U97" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="98" spans="1:24">
@@ -8178,10 +8182,10 @@
         <v>56</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>133</v>
@@ -8190,34 +8194,34 @@
         <v>15</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>230</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O98" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R98" s="17" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="S98" s="13">
         <v>45502</v>
@@ -8226,21 +8230,21 @@
         <v>46596</v>
       </c>
       <c r="U98" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="99" spans="1:24">
       <c r="A99" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>133</v>
@@ -8249,34 +8253,34 @@
         <v>15</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>256</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O99" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R99" s="17" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="S99" s="13">
         <v>45024</v>
@@ -8285,21 +8289,21 @@
         <v>46119</v>
       </c>
       <c r="U99" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="100" spans="1:24">
       <c r="A100" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>103</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>133</v>
@@ -8308,19 +8312,19 @@
         <v>15</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>276</v>
       </c>
       <c r="J100" s="9" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>20</v>
@@ -8329,13 +8333,13 @@
         <v>191</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R100" s="17" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="S100" s="13">
         <v>44980</v>
@@ -8344,12 +8348,12 @@
         <v>46075</v>
       </c>
       <c r="U100" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="101" spans="1:24">
       <c r="A101" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>113</v>
@@ -8358,7 +8362,7 @@
         <v>211</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>133</v>
@@ -8367,19 +8371,19 @@
         <v>15</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>285</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>211</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>20</v>
@@ -8388,13 +8392,13 @@
         <v>196</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q101" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R101" s="15" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="S101" s="13">
         <v>45517</v>
@@ -8403,7 +8407,7 @@
         <v>46611</v>
       </c>
       <c r="U101" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="102" spans="1:24">
@@ -8411,10 +8415,10 @@
         <v>122</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>133</v>
@@ -8423,34 +8427,34 @@
         <v>15</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>294</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O102" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="R102" s="17" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="S102" s="13">
         <v>44694</v>
@@ -8459,7 +8463,7 @@
         <v>45789</v>
       </c>
       <c r="U102" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="103" spans="1:24">
